--- a/XD_JIG/XCXD_Reliable_Test_JIG/Docs/timer_setting.xlsx
+++ b/XD_JIG/XCXD_Reliable_Test_JIG/Docs/timer_setting.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XCXD_Reliable_Test_JIG\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XCXD_Reliable_Test_JIG\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF42CCFB-E63B-4813-815B-2F2F975B8AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC71AE6B-E179-4C4C-8783-08B7F90FE0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{99A255A7-4B52-4891-88F0-7D8F7D35396C}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="28960" windowHeight="17440" xr2:uid="{99A255A7-4B52-4891-88F0-7D8F7D35396C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>TIM3</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,6 +75,30 @@
   </si>
   <si>
     <t>65ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xd ch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xd daisy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xd block</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>burst size</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repeat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>need ldim buff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -459,134 +483,177 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0DF5ED7-C43E-4ECB-8237-D9720F5A13AE}">
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <dimension ref="B2:K15"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A1" t="s">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B1">
+      <c r="C2">
         <v>72000000</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A2" t="s">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
+      <c r="C3">
         <v>144000000</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A4" t="s">
+      <c r="J3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="J4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
         <v>0</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A5" t="s">
+      <c r="J5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <f>K4*K3</f>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
         <v>1</v>
       </c>
-      <c r="B5">
-        <f>B1</f>
+      <c r="C6">
+        <f>C2</f>
         <v>72000000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A6" t="s">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
         <v>2</v>
       </c>
-      <c r="B6">
+      <c r="C7">
         <v>11</v>
       </c>
-      <c r="C6">
-        <f>B5/(B6+1)</f>
+      <c r="D7">
+        <f>C6/(C7+1)</f>
         <v>6000000</v>
       </c>
-      <c r="D6">
+      <c r="E7">
         <v>120</v>
       </c>
-      <c r="E6">
-        <f>C6/D6</f>
+      <c r="F7">
+        <f>D7/E7</f>
         <v>50000</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A7" t="s">
+      <c r="J7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
         <v>3</v>
       </c>
-      <c r="B7">
-        <f>E6-1</f>
+      <c r="C8">
+        <f>F7-1</f>
         <v>49999</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="B8">
-        <f>(B5/(B6+1))/(B7+1)</f>
+      <c r="J8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8">
+        <f>ROUNDUP(K5/K7, 0)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="C9">
+        <f>(C6/(C7+1))/(C8+1)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A10" t="s">
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9">
+        <f>K7*K8</f>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
         <v>4</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A11" t="s">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
         <v>1</v>
       </c>
-      <c r="B11">
-        <f>B1</f>
+      <c r="C12">
+        <f>C2</f>
         <v>72000000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A12" t="s">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
         <v>2</v>
       </c>
-      <c r="B12">
+      <c r="C13">
         <v>71</v>
       </c>
-      <c r="C12">
-        <f>B11/(B12+1)</f>
+      <c r="D13">
+        <f>C12/(C13+1)</f>
         <v>1000000</v>
       </c>
-      <c r="D12">
+      <c r="E13">
         <v>1000000</v>
       </c>
-      <c r="E12">
-        <f>C12/D12</f>
+      <c r="F13">
+        <f>D13/E13</f>
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A13" t="s">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
         <v>3</v>
       </c>
-      <c r="B13">
+      <c r="C14">
         <v>65535</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="B14">
-        <f>(B11/(B12+1))/(B13+1)</f>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="C15">
+        <f>(C12/(C13+1))/(C14+1)</f>
         <v>15.2587890625</v>
       </c>
-      <c r="C14">
-        <f>1000000/B14</f>
+      <c r="D15">
+        <f>1000000/C15</f>
         <v>65536</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E15" t="s">
         <v>9</v>
       </c>
     </row>
